--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Mistral-Small-3.2-24B-Instruct-2506/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Mistral-Small-3.2-24B-Instruct-2506/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.9318181818181818</v>
+        <v>0.9662921348314607</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.7746478873239436</v>
+        <v>0.7535211267605634</v>
       </c>
       <c r="D2">
-        <v>0.2807017543859649</v>
+        <v>0.2892561983471074</v>
       </c>
       <c r="E2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
